--- a/数据导出/item_prototypes.xlsx
+++ b/数据导出/item_prototypes.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,6 +1134,1152 @@
         <v>46129.37647059297</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>83</v>
+      </c>
+      <c r="B15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Inbound packets discarded</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>net.if.in.discards[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>84</v>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Inbound packets with errors</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>net.if.in.errors[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>85</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Bits received</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>net.if.in[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bps</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>86</v>
+      </c>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Outbound packets discarded</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>net.if.out.discards[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>87</v>
+      </c>
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Outbound packets with errors</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>net.if.out.errors[node_exporter"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>88</v>
+      </c>
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Bits sent</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>net.if.out[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>bps</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89</v>
+      </c>
+      <c r="B21" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Speed</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>net.if.speed[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sets value to 0 if metric is missing in node_exporter output.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>bps</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>90</v>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Operational status</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>net.if.status[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Reference: https://www.kernel.org/doc/Documentation/networking/operstates.txt</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Interface {#IFNAME}({#IFALIAS}): Interface type</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>net.if.type[node_exporter,"{#IFNAME}"]</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>node_network_protocol_type protocol_type value of /sys/class/net/&lt;iface&gt;.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>92</v>
+      </c>
+      <c r="B24" t="n">
+        <v>16</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk average queue size (avgqu-sz)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>vfs.dev.queue_size[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Current average disk queue, the number of requests outstanding on the disk at the time the performance data is collected.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>93</v>
+      </c>
+      <c r="B25" t="n">
+        <v>16</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk read request avg waiting time (r_await)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>vfs.dev.read.await[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>This formula contains two boolean expressions that evaluates to 1 or 0 in order to set calculated metric to zero and to avoid division by zero exception.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>!ms</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>7</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>94</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk read rate</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>vfs.dev.read.rate[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>r/s. The number (after merges) of read requests completed per second for the device.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>!r/s</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>7</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>95</v>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk read time (rate)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>vfs.dev.read.time.rate[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rate of total read time counter. Used in r_await calculation</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>7</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>96</v>
+      </c>
+      <c r="B28" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk utilization</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>vfs.dev.util[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>This item is the percentage of elapsed time that the selected disk drive was busy servicing read or writes requests.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>7</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>97</v>
+      </c>
+      <c r="B29" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk write request avg waiting time (w_await)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vfs.dev.write.await[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>This formula contains two boolean expressions that evaluates to 1 or 0 in order to set calculated metric to zero and to avoid division by zero exception.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>!ms</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O29" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>98</v>
+      </c>
+      <c r="B30" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk write rate</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>vfs.dev.write.rate[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>w/s. The number (after merges) of write requests completed per second for the device.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>!w/s</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>7</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O30" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>99</v>
+      </c>
+      <c r="B31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{#DEVNAME}: Disk write time (rate)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>vfs.dev.write.time.rate[node_exporter,"{#DEVNAME}"]</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rate of total write time counter. Used in w_await calculation</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O31" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>100</v>
+      </c>
+      <c r="B32" t="n">
+        <v>17</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Free space</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>vfs.fs.free[node_exporter,"{#FSNAME}"]</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O32" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>101</v>
+      </c>
+      <c r="B33" t="n">
+        <v>17</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Free inodes in %</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>vfs.fs.inode.pfree[node_exporter,"{#FSNAME}"]</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>102</v>
+      </c>
+      <c r="B34" t="n">
+        <v>17</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Space utilization</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>vfs.fs.pused[node_exporter,"{#FSNAME}"]</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Space utilization in % for {#FSNAME}</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O34" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>103</v>
+      </c>
+      <c r="B35" t="n">
+        <v>17</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Total space</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>vfs.fs.total[node_exporter,"{#FSNAME}"]</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Total space in Bytes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O35" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>104</v>
+      </c>
+      <c r="B36" t="n">
+        <v>17</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>{#FSNAME}: Used space</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>vfs.fs.used[node_exporter,"{#FSNAME}"]</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Used storage in Bytes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>7</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+      <c r="O36" s="1" t="n">
+        <v>46261.35537078948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
